--- a/diseases/d005/1980-1984.xlsx
+++ b/diseases/d005/1980-1984.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9803,9 +9734,6 @@
       </c>
       <c r="O48" t="n">
         <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>

--- a/diseases/d005/1980-1984.xlsx
+++ b/diseases/d005/1980-1984.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,19 +751,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -907,38 +907,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>Acquired Immune Deficiency Syndrome</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1200,42 +1200,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>Acquired Immune Deficiency Syndrome</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1434,42 +1434,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1531,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1687,19 +1692,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1801,7 +1806,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1921,12 +1931,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1957,7 +1967,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,12 +2092,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2191,7 +2206,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,12 +2331,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2347,7 +2367,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,12 +2492,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2581,7 +2606,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,12 +2731,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2737,7 +2767,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,12 +2892,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2971,7 +3006,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,12 +3131,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3127,7 +3167,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,12 +3292,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3361,7 +3406,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,19 +3531,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3517,7 +3567,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,19 +3692,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3751,7 +3806,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,12 +3931,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3907,7 +3967,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,12 +4092,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4141,7 +4206,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,19 +4331,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4297,7 +4367,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,19 +4492,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4531,7 +4606,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,12 +4731,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4687,7 +4767,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,12 +4892,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4921,7 +5006,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,12 +5131,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5077,7 +5167,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,12 +5292,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5311,7 +5406,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,12 +5531,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5467,7 +5567,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,12 +5692,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5701,7 +5806,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5821,12 +5931,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5857,7 +5967,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5977,12 +6092,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -6091,7 +6206,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6181,12 +6301,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6211,19 +6331,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6232,12 +6352,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -6257,7 +6377,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -6270,42 +6390,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6457,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6367,38 +6487,38 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>Acquired Immune Deficiency Syndrome</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -6408,12 +6528,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -6423,7 +6543,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6458,17 +6578,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6491,7 +6611,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D86_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -6504,42 +6624,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6721,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6637,7 +6757,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6757,12 +6882,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6871,7 +6996,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6991,19 +7121,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7027,7 +7157,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7147,19 +7282,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7261,7 +7396,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7381,12 +7521,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7417,7 +7557,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,12 +7682,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7651,7 +7796,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,12 +7921,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7807,7 +7957,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,12 +8082,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8041,7 +8196,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,12 +8321,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8197,7 +8357,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,12 +8482,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8431,7 +8596,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,19 +8721,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8587,7 +8757,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,19 +8882,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8821,7 +8996,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,12 +9121,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -8977,7 +9157,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,12 +9282,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -9211,7 +9396,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,19 +9521,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-08</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9367,7 +9557,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,19 +9682,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-08</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9601,7 +9796,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,12 +9921,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-09-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-09</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9757,7 +9957,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,12 +10082,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-09-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -9991,7 +10196,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,55 +10204,1260 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
         <v>1</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA49" t="inlineStr">
+      <c r="BA51" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr">
+      <c r="BB51" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -10098,7 +11508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
     </row>
@@ -10169,7 +11579,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -10179,7 +11589,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -10199,7 +11609,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -10209,7 +11619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -10231,7 +11641,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16">
